--- a/test_numeric_ship_employee_ids.xlsx
+++ b/test_numeric_ship_employee_ids.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>_11110099</t>
+          <t>_11100001</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -141,7 +141,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>_11110098</t>
+          <t>_11100002</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -173,7 +173,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>_11110097</t>
+          <t>_11100003</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -205,7 +205,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>_11110096</t>
+          <t>_11100004</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -237,7 +237,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>_11110095</t>
+          <t>_11100005</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -269,7 +269,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>_11110094</t>
+          <t>_11100006</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -301,7 +301,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>_11110093</t>
+          <t>_11100007</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -333,7 +333,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>_11110092</t>
+          <t>_11100008</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -365,7 +365,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>_11210099</t>
+          <t>_11200009</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -397,7 +397,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>_11210098</t>
+          <t>_11200010</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -429,7 +429,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>_11210097</t>
+          <t>_11200011</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -461,7 +461,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>_11210096</t>
+          <t>_11200012</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -493,7 +493,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>_11210095</t>
+          <t>_11200013</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>_11210094</t>
+          <t>_11200014</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>_11210093</t>
+          <t>_11200015</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>_11210092</t>
+          <t>_11200016</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>_11310099</t>
+          <t>_11300017</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>_11310098</t>
+          <t>_11300018</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>_11310097</t>
+          <t>_11300019</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>_11310096</t>
+          <t>_11300020</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>_11310095</t>
+          <t>_11300021</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>_11310094</t>
+          <t>_11300022</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>_11310093</t>
+          <t>_11300023</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>_11310092</t>
+          <t>_11300024</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">

--- a/test_numeric_ship_employee_ids.xlsx
+++ b/test_numeric_ship_employee_ids.xlsx
@@ -94,7 +94,7 @@
     <row r="2">
       <c r="C2" t="inlineStr">
         <is>
-          <t>_00001</t>
+          <t>00001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -104,12 +104,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>_111</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>_11100001</t>
+          <t>11100001</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -126,7 +126,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>_00002</t>
+          <t>00002</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -136,12 +136,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>_111</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>_11100002</t>
+          <t>11100002</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -158,7 +158,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>_00003</t>
+          <t>00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -168,12 +168,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>_111</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>_11100003</t>
+          <t>11100003</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -190,7 +190,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>_00004</t>
+          <t>00004</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -200,12 +200,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>_111</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>_11100004</t>
+          <t>11100004</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -222,7 +222,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>_00005</t>
+          <t>00005</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -232,12 +232,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>_111</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>_11100005</t>
+          <t>11100005</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -254,7 +254,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>_00006</t>
+          <t>00006</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -264,12 +264,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>_111</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>_11100006</t>
+          <t>11100006</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -286,7 +286,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>_00007</t>
+          <t>00007</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -296,12 +296,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>_111</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>_11100007</t>
+          <t>11100007</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -318,7 +318,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>_00008</t>
+          <t>00008</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -328,12 +328,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>_111</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>_11100008</t>
+          <t>11100008</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -350,7 +350,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>_00009</t>
+          <t>00009</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -360,12 +360,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>_112</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>_11200009</t>
+          <t>11200009</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -382,7 +382,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>_00010</t>
+          <t>00010</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -392,12 +392,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>_112</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>_11200010</t>
+          <t>11200010</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -414,7 +414,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>_00011</t>
+          <t>00011</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -424,12 +424,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>_112</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>_11200011</t>
+          <t>11200011</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -446,7 +446,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>_00012</t>
+          <t>00012</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>_112</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>_11200012</t>
+          <t>11200012</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -478,7 +478,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>_00013</t>
+          <t>00013</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -488,12 +488,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>_112</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>_11200013</t>
+          <t>11200013</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -510,7 +510,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>_00014</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -520,12 +520,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>_112</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>_11200014</t>
+          <t>11200014</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -542,7 +542,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>_00015</t>
+          <t>00015</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>_112</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>_11200015</t>
+          <t>11200015</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -574,7 +574,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>_00016</t>
+          <t>00016</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -584,12 +584,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>_112</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>_11200016</t>
+          <t>11200016</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -606,7 +606,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>_00017</t>
+          <t>00017</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -616,12 +616,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>_113</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>_11300017</t>
+          <t>11300017</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -638,7 +638,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>_00018</t>
+          <t>00018</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>_113</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>_11300018</t>
+          <t>11300018</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>_00019</t>
+          <t>00019</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -680,12 +680,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>_113</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>_11300019</t>
+          <t>11300019</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>_00020</t>
+          <t>00020</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>_113</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>_11300020</t>
+          <t>11300020</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>_00021</t>
+          <t>00021</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>_113</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>_11300021</t>
+          <t>11300021</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>_00022</t>
+          <t>00022</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>_113</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>_11300022</t>
+          <t>11300022</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -798,7 +798,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>_00023</t>
+          <t>00023</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>_113</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>_11300023</t>
+          <t>11300023</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>_00024</t>
+          <t>00024</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -840,12 +840,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>_113</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>_11300024</t>
+          <t>11300024</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
